--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
@@ -94,18 +94,6 @@
     <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
@@ -904,6 +892,12 @@
     <t xml:space="preserve">Renca</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">13105</t>
   </si>
   <si>
@@ -1288,6 +1282,12 @@
     <t xml:space="preserve">Arica</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4106</t>
   </si>
   <si>
@@ -2128,7 +2128,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:18</t>
+    <t xml:space="preserve">2026-09-09 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2768,7 +2768,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>78.03</v>
+        <v>77.14</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2800,7 +2800,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>77.37</v>
+        <v>77.09</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2832,7 +2832,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>77.14</v>
+        <v>76.45</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2843,10 +2843,10 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>31</v>
@@ -2864,7 +2864,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>77.09</v>
+        <v>76.19</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2896,7 +2896,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>76.45</v>
+        <v>76.02</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2928,7 +2928,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>76.19</v>
+        <v>75.37</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2960,7 +2960,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>76.02</v>
+        <v>74.51</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2971,10 +2971,10 @@
         <v>2018</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -2992,7 +2992,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>75.37</v>
+        <v>73.43</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -3003,10 +3003,10 @@
         <v>2018</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>41</v>
@@ -3024,7 +3024,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>74.51</v>
+        <v>72.92</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -3035,10 +3035,10 @@
         <v>2018</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>43</v>
@@ -3056,7 +3056,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>73.43</v>
+        <v>72.64</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -3067,28 +3067,28 @@
         <v>2018</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>72.92</v>
+        <v>78.46</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3099,28 +3099,28 @@
         <v>2018</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>72.64</v>
+        <v>77.98</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3131,28 +3131,28 @@
         <v>2018</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>78.46</v>
+        <v>77.14</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3163,10 +3163,10 @@
         <v>2018</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
@@ -3175,16 +3175,16 @@
         <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>77.98</v>
+        <v>77.1</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3198,7 +3198,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>57</v>
@@ -3207,16 +3207,16 @@
         <v>58</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>77.14</v>
+        <v>76.79</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3227,28 +3227,28 @@
         <v>2018</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>77.1</v>
+        <v>76.68</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3262,25 +3262,25 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>76.79</v>
+        <v>76.53</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3291,10 +3291,10 @@
         <v>2018</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>64</v>
@@ -3303,16 +3303,16 @@
         <v>65</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>76.68</v>
+        <v>76.35</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3323,28 +3323,28 @@
         <v>2018</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>76.53</v>
+        <v>76.34</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3355,28 +3355,28 @@
         <v>2018</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>76.35</v>
+        <v>76.33</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3387,28 +3387,28 @@
         <v>2018</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>76.34</v>
+        <v>75.96</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3422,7 +3422,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3431,16 +3431,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>76.33</v>
+        <v>75.93</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3454,7 +3454,7 @@
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3463,16 +3463,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>75.96</v>
+        <v>75.89</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3483,10 +3483,10 @@
         <v>2018</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3495,16 +3495,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>75.93</v>
+        <v>75.72</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3515,10 +3515,10 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3527,16 +3527,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>75.89</v>
+        <v>75.32</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3550,7 +3550,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3559,16 +3559,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>75.72</v>
+        <v>75.3</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3582,7 +3582,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3591,16 +3591,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>75.32</v>
+        <v>75.2</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3611,10 +3611,10 @@
         <v>2018</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3623,16 +3623,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3643,10 +3643,10 @@
         <v>2018</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3655,16 +3655,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>75.2</v>
+        <v>75.13</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3675,10 +3675,10 @@
         <v>2018</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3687,16 +3687,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>75.2</v>
+        <v>74.88</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3707,10 +3707,10 @@
         <v>2018</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3719,16 +3719,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>75.13</v>
+        <v>74.88</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3739,10 +3739,10 @@
         <v>2018</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3751,16 +3751,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>74.88</v>
+        <v>74.87</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3771,10 +3771,10 @@
         <v>2018</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3783,16 +3783,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>74.88</v>
+        <v>74.79</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3806,7 +3806,7 @@
         <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3815,16 +3815,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>74.87</v>
+        <v>74.77</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3835,10 +3835,10 @@
         <v>2018</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3847,16 +3847,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>74.79</v>
+        <v>74.76</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3867,10 +3867,10 @@
         <v>2018</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3879,16 +3879,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>74.77</v>
+        <v>74.74</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3899,10 +3899,10 @@
         <v>2018</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3911,16 +3911,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>74.76</v>
+        <v>74.74</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3931,10 +3931,10 @@
         <v>2018</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3943,16 +3943,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>74.74</v>
+        <v>74.68</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3963,10 +3963,10 @@
         <v>2018</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3975,16 +3975,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>74.74</v>
+        <v>74.62</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -3995,10 +3995,10 @@
         <v>2018</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -4007,16 +4007,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>74.68</v>
+        <v>74.39</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -4027,10 +4027,10 @@
         <v>2018</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -4039,16 +4039,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>74.62</v>
+        <v>74.22</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -4059,10 +4059,10 @@
         <v>2018</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -4071,16 +4071,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>74.39</v>
+        <v>74.19</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4091,10 +4091,10 @@
         <v>2018</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -4103,16 +4103,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>74.22</v>
+        <v>74.18</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4123,10 +4123,10 @@
         <v>2018</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -4135,16 +4135,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>74.19</v>
+        <v>74.14</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -4158,7 +4158,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -4167,16 +4167,16 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>74.18</v>
+        <v>74.12</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -4187,10 +4187,10 @@
         <v>2018</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -4199,16 +4199,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>74.14</v>
+        <v>74.07</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4219,28 +4219,28 @@
         <v>2018</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>74.12</v>
+        <v>74.05</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4251,28 +4251,28 @@
         <v>2018</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>74.07</v>
+        <v>73.93</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -4283,28 +4283,28 @@
         <v>2018</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>74.05</v>
+        <v>73.91</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -4315,10 +4315,10 @@
         <v>2018</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4327,16 +4327,16 @@
         <v>130</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>73.93</v>
+        <v>73.87</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4347,10 +4347,10 @@
         <v>2018</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4359,16 +4359,16 @@
         <v>132</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>73.91</v>
+        <v>73.86</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4379,10 +4379,10 @@
         <v>2018</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4391,16 +4391,16 @@
         <v>134</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>73.87</v>
+        <v>73.85</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4411,10 +4411,10 @@
         <v>2018</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4423,16 +4423,16 @@
         <v>136</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>73.86</v>
+        <v>73.82</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4443,10 +4443,10 @@
         <v>2018</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>137</v>
@@ -4455,16 +4455,16 @@
         <v>138</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>73.85</v>
+        <v>73.78</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -4478,7 +4478,7 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>139</v>
@@ -4487,16 +4487,16 @@
         <v>140</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>73.82</v>
+        <v>73.77</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4507,10 +4507,10 @@
         <v>2018</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>141</v>
@@ -4519,16 +4519,16 @@
         <v>142</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>73.78</v>
+        <v>73.72</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4539,10 +4539,10 @@
         <v>2018</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>143</v>
@@ -4551,16 +4551,16 @@
         <v>144</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>73.77</v>
+        <v>73.62</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4571,10 +4571,10 @@
         <v>2018</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>145</v>
@@ -4583,16 +4583,16 @@
         <v>146</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>73.72</v>
+        <v>73.61</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4603,10 +4603,10 @@
         <v>2018</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4615,16 +4615,16 @@
         <v>148</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>73.62</v>
+        <v>73.59</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4635,10 +4635,10 @@
         <v>2018</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>149</v>
@@ -4647,16 +4647,16 @@
         <v>150</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>73.61</v>
+        <v>73.58</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4667,10 +4667,10 @@
         <v>2018</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>151</v>
@@ -4679,16 +4679,16 @@
         <v>152</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>73.59</v>
+        <v>73.55</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4699,10 +4699,10 @@
         <v>2018</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>153</v>
@@ -4711,16 +4711,16 @@
         <v>154</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>73.58</v>
+        <v>73.53</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4731,10 +4731,10 @@
         <v>2018</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4743,16 +4743,16 @@
         <v>156</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>73.55</v>
+        <v>73.52</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4763,10 +4763,10 @@
         <v>2018</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>157</v>
@@ -4775,16 +4775,16 @@
         <v>158</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>73.53</v>
+        <v>73.47</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4795,10 +4795,10 @@
         <v>2018</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>159</v>
@@ -4807,16 +4807,16 @@
         <v>160</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>73.52</v>
+        <v>73.4</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4827,10 +4827,10 @@
         <v>2018</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4839,16 +4839,16 @@
         <v>162</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>73.47</v>
+        <v>73.36</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4859,10 +4859,10 @@
         <v>2018</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4871,16 +4871,16 @@
         <v>164</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>73.4</v>
+        <v>73.31</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4891,10 +4891,10 @@
         <v>2018</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4903,16 +4903,16 @@
         <v>166</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>73.36</v>
+        <v>73.29</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4923,10 +4923,10 @@
         <v>2018</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>167</v>
@@ -4935,16 +4935,16 @@
         <v>168</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>73.31</v>
+        <v>73.26</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4955,10 +4955,10 @@
         <v>2018</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -4967,16 +4967,16 @@
         <v>170</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>73.29</v>
+        <v>73.24</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>15</v>
@@ -4987,10 +4987,10 @@
         <v>2018</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -4999,16 +4999,16 @@
         <v>172</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>73.26</v>
+        <v>73.23</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -5019,10 +5019,10 @@
         <v>2018</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>173</v>
@@ -5031,16 +5031,16 @@
         <v>174</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>73.24</v>
+        <v>73.23</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -5054,7 +5054,7 @@
         <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>175</v>
@@ -5063,16 +5063,16 @@
         <v>176</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>73.23</v>
+        <v>73.22</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -5083,10 +5083,10 @@
         <v>2018</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>177</v>
@@ -5095,16 +5095,16 @@
         <v>178</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>73.23</v>
+        <v>73.2</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5115,10 +5115,10 @@
         <v>2018</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>179</v>
@@ -5127,16 +5127,16 @@
         <v>180</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>73.22</v>
+        <v>73.13</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5147,10 +5147,10 @@
         <v>2018</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>181</v>
@@ -5159,16 +5159,16 @@
         <v>182</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>73.2</v>
+        <v>72.95</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -5182,7 +5182,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>183</v>
@@ -5191,16 +5191,16 @@
         <v>184</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>73.13</v>
+        <v>72.91</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5211,10 +5211,10 @@
         <v>2018</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>185</v>
@@ -5223,16 +5223,16 @@
         <v>186</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>72.95</v>
+        <v>72.88</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5243,10 +5243,10 @@
         <v>2018</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>187</v>
@@ -5255,16 +5255,16 @@
         <v>188</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>72.91</v>
+        <v>72.85</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -5275,10 +5275,10 @@
         <v>2018</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>189</v>
@@ -5287,16 +5287,16 @@
         <v>190</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>72.88</v>
+        <v>72.71</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -5307,10 +5307,10 @@
         <v>2018</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>191</v>
@@ -5319,16 +5319,16 @@
         <v>192</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>72.85</v>
+        <v>72.71</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -5342,7 +5342,7 @@
         <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>193</v>
@@ -5351,10 +5351,10 @@
         <v>194</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5371,10 +5371,10 @@
         <v>2018</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>195</v>
@@ -5383,16 +5383,16 @@
         <v>196</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>72.71</v>
+        <v>72.67</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5403,10 +5403,10 @@
         <v>2018</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>197</v>
@@ -5415,16 +5415,16 @@
         <v>198</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>72.71</v>
+        <v>72.66</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -5435,10 +5435,10 @@
         <v>2018</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>199</v>
@@ -5447,16 +5447,16 @@
         <v>200</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>72.67</v>
+        <v>72.61</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -5467,10 +5467,10 @@
         <v>2018</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>201</v>
@@ -5479,16 +5479,16 @@
         <v>202</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>72.66</v>
+        <v>72.6</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5499,10 +5499,10 @@
         <v>2018</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>203</v>
@@ -5511,16 +5511,16 @@
         <v>204</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>72.61</v>
+        <v>72.59</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5531,10 +5531,10 @@
         <v>2018</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>205</v>
@@ -5543,16 +5543,16 @@
         <v>206</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>72.6</v>
+        <v>72.59</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5563,10 +5563,10 @@
         <v>2018</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>207</v>
@@ -5575,16 +5575,16 @@
         <v>208</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>72.59</v>
+        <v>72.57</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5595,10 +5595,10 @@
         <v>2018</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>209</v>
@@ -5607,16 +5607,16 @@
         <v>210</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>72.59</v>
+        <v>72.56</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5627,10 +5627,10 @@
         <v>2018</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>211</v>
@@ -5639,16 +5639,16 @@
         <v>212</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>72.57</v>
+        <v>72.53</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5659,10 +5659,10 @@
         <v>2018</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>213</v>
@@ -5671,16 +5671,16 @@
         <v>214</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>72.56</v>
+        <v>72.53</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5691,10 +5691,10 @@
         <v>2018</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>215</v>
@@ -5703,16 +5703,16 @@
         <v>216</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>72.53</v>
+        <v>72.52</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5723,10 +5723,10 @@
         <v>2018</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>217</v>
@@ -5735,16 +5735,16 @@
         <v>218</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>72.53</v>
+        <v>72.52</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5755,10 +5755,10 @@
         <v>2018</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>219</v>
@@ -5767,10 +5767,10 @@
         <v>220</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5790,7 +5790,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>221</v>
@@ -5799,16 +5799,16 @@
         <v>222</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>72.52</v>
+        <v>72.42</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5822,7 +5822,7 @@
         <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>223</v>
@@ -5831,16 +5831,16 @@
         <v>224</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>72.52</v>
+        <v>72.4</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5851,10 +5851,10 @@
         <v>2018</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>225</v>
@@ -5863,16 +5863,16 @@
         <v>226</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>72.42</v>
+        <v>72.4</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5886,7 +5886,7 @@
         <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>227</v>
@@ -5895,16 +5895,16 @@
         <v>228</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>72.4</v>
+        <v>72.38</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5918,7 +5918,7 @@
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>229</v>
@@ -5927,16 +5927,16 @@
         <v>230</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>72.4</v>
+        <v>72.36</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5947,10 +5947,10 @@
         <v>2018</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>231</v>
@@ -5959,16 +5959,16 @@
         <v>232</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>72.38</v>
+        <v>72.24</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5979,10 +5979,10 @@
         <v>2018</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>233</v>
@@ -5991,16 +5991,16 @@
         <v>234</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>72.36</v>
+        <v>72.21</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -6011,10 +6011,10 @@
         <v>2018</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>235</v>
@@ -6023,16 +6023,16 @@
         <v>236</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>72.24</v>
+        <v>72.07</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -6043,10 +6043,10 @@
         <v>2018</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>237</v>
@@ -6055,16 +6055,16 @@
         <v>238</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>72.21</v>
+        <v>72.06</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -6078,7 +6078,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>239</v>
@@ -6087,16 +6087,16 @@
         <v>240</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>72.07</v>
+        <v>72.06</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -6110,7 +6110,7 @@
         <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>241</v>
@@ -6119,16 +6119,16 @@
         <v>242</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>72.06</v>
+        <v>72.01</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -6139,10 +6139,10 @@
         <v>2018</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>243</v>
@@ -6151,16 +6151,16 @@
         <v>244</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>72.06</v>
+        <v>71.99</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6174,7 +6174,7 @@
         <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>245</v>
@@ -6183,16 +6183,16 @@
         <v>246</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>72.01</v>
+        <v>71.92</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>15</v>
@@ -6203,10 +6203,10 @@
         <v>2018</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>247</v>
@@ -6215,16 +6215,16 @@
         <v>248</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>71.99</v>
+        <v>71.91</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>15</v>
@@ -6235,10 +6235,10 @@
         <v>2018</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>249</v>
@@ -6247,16 +6247,16 @@
         <v>250</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>71.92</v>
+        <v>71.91</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6267,10 +6267,10 @@
         <v>2018</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>251</v>
@@ -6279,16 +6279,16 @@
         <v>252</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>71.91</v>
+        <v>71.9</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -6299,10 +6299,10 @@
         <v>2018</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>253</v>
@@ -6311,16 +6311,16 @@
         <v>254</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>71.91</v>
+        <v>71.87</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6331,10 +6331,10 @@
         <v>2018</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>255</v>
@@ -6343,16 +6343,16 @@
         <v>256</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>71.9</v>
+        <v>71.82</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -6363,10 +6363,10 @@
         <v>2018</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>257</v>
@@ -6375,16 +6375,16 @@
         <v>258</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>71.87</v>
+        <v>71.81</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6398,7 +6398,7 @@
         <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>259</v>
@@ -6407,16 +6407,16 @@
         <v>260</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>71.82</v>
+        <v>71.79</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -6427,10 +6427,10 @@
         <v>2018</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>261</v>
@@ -6439,16 +6439,16 @@
         <v>262</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>71.81</v>
+        <v>71.77</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6459,10 +6459,10 @@
         <v>2018</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>263</v>
@@ -6471,16 +6471,16 @@
         <v>264</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>71.79</v>
+        <v>71.72</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6494,7 +6494,7 @@
         <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>265</v>
@@ -6503,16 +6503,16 @@
         <v>266</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>71.77</v>
+        <v>71.66</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6523,10 +6523,10 @@
         <v>2018</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>267</v>
@@ -6535,16 +6535,16 @@
         <v>268</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>71.72</v>
+        <v>71.64</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6558,7 +6558,7 @@
         <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>269</v>
@@ -6567,16 +6567,16 @@
         <v>270</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>71.66</v>
+        <v>71.6</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6590,7 +6590,7 @@
         <v>16</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>271</v>
@@ -6599,16 +6599,16 @@
         <v>272</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>71.64</v>
+        <v>71.58</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6622,7 +6622,7 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>273</v>
@@ -6631,16 +6631,16 @@
         <v>274</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>71.6</v>
+        <v>71.51</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6651,10 +6651,10 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>275</v>
@@ -6663,16 +6663,16 @@
         <v>276</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>71.58</v>
+        <v>71.5</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6683,10 +6683,10 @@
         <v>2018</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>277</v>
@@ -6695,16 +6695,16 @@
         <v>278</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>71.51</v>
+        <v>71.48</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6715,10 +6715,10 @@
         <v>2018</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>279</v>
@@ -6727,16 +6727,16 @@
         <v>280</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>71.5</v>
+        <v>71.46</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6747,10 +6747,10 @@
         <v>2018</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6759,16 +6759,16 @@
         <v>282</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>71.48</v>
+        <v>71.44</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6779,10 +6779,10 @@
         <v>2018</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>283</v>
@@ -6791,16 +6791,16 @@
         <v>284</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>71.46</v>
+        <v>71.42</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>15</v>
@@ -6811,10 +6811,10 @@
         <v>2018</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>285</v>
@@ -6823,16 +6823,16 @@
         <v>286</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>71.44</v>
+        <v>71.41</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6846,7 +6846,7 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6855,16 +6855,16 @@
         <v>288</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>71.42</v>
+        <v>71.37</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>15</v>
@@ -6878,7 +6878,7 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6887,16 +6887,16 @@
         <v>290</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>71.41</v>
+        <v>71.33</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6907,10 +6907,10 @@
         <v>2018</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>291</v>
@@ -6919,16 +6919,16 @@
         <v>292</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>71.37</v>
+        <v>71.33</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6942,7 +6942,7 @@
         <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>293</v>
@@ -6951,16 +6951,16 @@
         <v>294</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>71.33</v>
+        <v>71.31</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6971,10 +6971,10 @@
         <v>2018</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>295</v>
@@ -6983,16 +6983,16 @@
         <v>296</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>71.31</v>
+        <v>71.3</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -7003,10 +7003,10 @@
         <v>2018</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>297</v>
@@ -7015,16 +7015,16 @@
         <v>298</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>71.3</v>
+        <v>71.23</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>15</v>
@@ -7035,10 +7035,10 @@
         <v>2018</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -7047,16 +7047,16 @@
         <v>300</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>71.23</v>
+        <v>71.2</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -7067,10 +7067,10 @@
         <v>2018</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7079,16 +7079,16 @@
         <v>302</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>71.2</v>
+        <v>71.18</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>15</v>
@@ -7102,7 +7102,7 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7111,16 +7111,16 @@
         <v>304</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>71.18</v>
+        <v>71.14</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7134,7 +7134,7 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7143,16 +7143,16 @@
         <v>306</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>71.14</v>
+        <v>71.08</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>15</v>
@@ -7163,10 +7163,10 @@
         <v>2018</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7175,10 +7175,10 @@
         <v>308</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7195,10 +7195,10 @@
         <v>2018</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7207,16 +7207,16 @@
         <v>310</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>71.08</v>
+        <v>71.06</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>15</v>
@@ -7227,10 +7227,10 @@
         <v>2018</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7239,16 +7239,16 @@
         <v>312</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>71.06</v>
+        <v>71.04</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7259,10 +7259,10 @@
         <v>2018</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>313</v>
@@ -7271,16 +7271,16 @@
         <v>314</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>71.04</v>
+        <v>71.03</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -7294,7 +7294,7 @@
         <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7303,16 +7303,16 @@
         <v>316</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>71.03</v>
+        <v>71.01</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7323,10 +7323,10 @@
         <v>2018</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7335,10 +7335,10 @@
         <v>318</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7355,10 +7355,10 @@
         <v>2018</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7367,16 +7367,16 @@
         <v>320</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>71.01</v>
+        <v>70.97</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>15</v>
@@ -7387,10 +7387,10 @@
         <v>2018</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7399,16 +7399,16 @@
         <v>322</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>70.97</v>
+        <v>70.7</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -7419,10 +7419,10 @@
         <v>2018</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7431,16 +7431,16 @@
         <v>324</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>70.7</v>
+        <v>70.68</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -7451,10 +7451,10 @@
         <v>2018</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7463,16 +7463,16 @@
         <v>326</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>70.68</v>
+        <v>70.58</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>15</v>
@@ -7486,7 +7486,7 @@
         <v>16</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7495,16 +7495,16 @@
         <v>328</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>70.58</v>
+        <v>70.57</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7515,10 +7515,10 @@
         <v>2018</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7527,16 +7527,16 @@
         <v>330</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>70.57</v>
+        <v>70.46</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>15</v>
@@ -7550,7 +7550,7 @@
         <v>13</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>331</v>
@@ -7559,16 +7559,16 @@
         <v>332</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>70.46</v>
+        <v>70.45</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>15</v>
@@ -7579,10 +7579,10 @@
         <v>2018</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>333</v>
@@ -7591,10 +7591,10 @@
         <v>334</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7611,10 +7611,10 @@
         <v>2018</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>335</v>
@@ -7623,16 +7623,16 @@
         <v>336</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>70.45</v>
+        <v>70.41</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7643,10 +7643,10 @@
         <v>2018</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7655,10 +7655,10 @@
         <v>338</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7678,7 +7678,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7687,16 +7687,16 @@
         <v>340</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>70.41</v>
+        <v>70.23</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7707,10 +7707,10 @@
         <v>2018</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7719,16 +7719,16 @@
         <v>342</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7739,10 +7739,10 @@
         <v>2018</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7751,10 +7751,10 @@
         <v>344</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7771,10 +7771,10 @@
         <v>2018</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7783,16 +7783,16 @@
         <v>346</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>70.22</v>
+        <v>70.21</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7803,10 +7803,10 @@
         <v>2018</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7815,16 +7815,16 @@
         <v>348</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>70.21</v>
+        <v>70.2</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7835,10 +7835,10 @@
         <v>2018</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7847,16 +7847,16 @@
         <v>350</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>70.2</v>
+        <v>70.09</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7867,10 +7867,10 @@
         <v>2018</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7879,16 +7879,16 @@
         <v>352</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>70.09</v>
+        <v>70.05</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7902,7 +7902,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7911,16 +7911,16 @@
         <v>354</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>70.05</v>
+        <v>69.95</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7931,10 +7931,10 @@
         <v>2018</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7943,16 +7943,16 @@
         <v>356</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>69.95</v>
+        <v>69.93</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7963,10 +7963,10 @@
         <v>2018</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -7975,16 +7975,16 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>69.93</v>
+        <v>69.56</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -7995,10 +7995,10 @@
         <v>2018</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -8007,16 +8007,16 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>69.56</v>
+        <v>69.47</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -8027,10 +8027,10 @@
         <v>2018</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8039,16 +8039,16 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>69.47</v>
+        <v>69.36</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -8059,10 +8059,10 @@
         <v>2018</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8071,16 +8071,16 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>69.36</v>
+        <v>69.31</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>15</v>
@@ -8091,10 +8091,10 @@
         <v>2018</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8103,16 +8103,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>69.31</v>
+        <v>69.06</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8123,10 +8123,10 @@
         <v>2018</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8135,16 +8135,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>69.06</v>
+        <v>68.69</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8158,7 +8158,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8167,16 +8167,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>68.69</v>
+        <v>68.61</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8190,7 +8190,7 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8199,16 +8199,16 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>68.61</v>
+        <v>68.55</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -8219,10 +8219,10 @@
         <v>2018</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8231,16 +8231,16 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>68.55</v>
+        <v>68.51</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -8251,10 +8251,10 @@
         <v>2018</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8263,16 +8263,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>68.51</v>
+        <v>68.39</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8286,7 +8286,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8295,16 +8295,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>68.39</v>
+        <v>67.52</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8318,7 +8318,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8327,16 +8327,16 @@
         <v>380</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>67.52</v>
+        <v>67.41</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8350,7 +8350,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8359,16 +8359,16 @@
         <v>382</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>67.41</v>
+        <v>66.05</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8382,7 +8382,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>383</v>
@@ -8391,16 +8391,16 @@
         <v>384</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>66.05</v>
+        <v>65.52</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -8414,7 +8414,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>385</v>
@@ -8423,16 +8423,16 @@
         <v>386</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>65.52</v>
+        <v>65.29</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8446,7 +8446,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>387</v>
@@ -8455,16 +8455,16 @@
         <v>388</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>65.29</v>
+        <v>64.45</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8478,7 +8478,7 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>389</v>
@@ -8487,16 +8487,16 @@
         <v>390</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>64.45</v>
+        <v>62.6</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8510,7 +8510,7 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>391</v>
@@ -8519,16 +8519,16 @@
         <v>392</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>62.6</v>
+        <v>55.29</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8542,7 +8542,7 @@
         <v>13</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>393</v>
@@ -8551,16 +8551,16 @@
         <v>394</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>55.29</v>
+        <v>53.22</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8571,28 +8571,28 @@
         <v>2018</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>49</v>
+        <v>395</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>52</v>
+        <v>398</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>53</v>
+        <v>399</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>53.22</v>
+        <v>77.25</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8603,28 +8603,28 @@
         <v>2018</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E190" s="2" t="s">
+      <c r="G190" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F190" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>77.25</v>
+        <v>76.38</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8638,7 +8638,7 @@
         <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>403</v>
@@ -8647,16 +8647,16 @@
         <v>404</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>76.38</v>
+        <v>76.33</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8667,10 +8667,10 @@
         <v>2018</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>405</v>
@@ -8679,16 +8679,16 @@
         <v>406</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>76.33</v>
+        <v>76</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8702,7 +8702,7 @@
         <v>3</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>407</v>
@@ -8711,16 +8711,16 @@
         <v>408</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>76</v>
+        <v>75.89</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8731,28 +8731,28 @@
         <v>2018</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>75.89</v>
+        <v>75.86</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8763,10 +8763,10 @@
         <v>2018</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>412</v>
@@ -8775,16 +8775,16 @@
         <v>413</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>75.86</v>
+        <v>75.41</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8798,25 +8798,25 @@
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>414</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>75.41</v>
+        <v>75.18</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8827,28 +8827,28 @@
         <v>2018</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D197" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="E197" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="F197" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>75.18</v>
+        <v>74.8</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8859,10 +8859,10 @@
         <v>2018</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>417</v>
@@ -8871,16 +8871,16 @@
         <v>418</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>74.8</v>
+        <v>74.24</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8891,10 +8891,10 @@
         <v>2018</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>419</v>
@@ -8903,16 +8903,16 @@
         <v>420</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>74.24</v>
+        <v>73.97</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8923,10 +8923,10 @@
         <v>2018</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>421</v>
@@ -8935,16 +8935,16 @@
         <v>422</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>73.97</v>
+        <v>73.96</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8958,7 +8958,7 @@
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>423</v>
@@ -8967,10 +8967,10 @@
         <v>424</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8990,7 +8990,7 @@
         <v>3</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>425</v>
@@ -8999,10 +8999,10 @@
         <v>426</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -9022,7 +9022,7 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>427</v>
@@ -9031,10 +9031,10 @@
         <v>428</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9063,10 +9063,10 @@
         <v>431</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9086,7 +9086,7 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>432</v>
@@ -9095,10 +9095,10 @@
         <v>433</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9118,7 +9118,7 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>434</v>
@@ -9127,10 +9127,10 @@
         <v>435</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9159,10 +9159,10 @@
         <v>437</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9182,7 +9182,7 @@
         <v>3</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>438</v>
@@ -9191,10 +9191,10 @@
         <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9214,7 +9214,7 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>440</v>
@@ -9223,10 +9223,10 @@
         <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9255,10 +9255,10 @@
         <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9287,10 +9287,10 @@
         <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9310,7 +9310,7 @@
         <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>447</v>
@@ -9319,10 +9319,10 @@
         <v>448</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9342,7 +9342,7 @@
         <v>3</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>449</v>
@@ -9351,10 +9351,10 @@
         <v>450</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9374,7 +9374,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>451</v>
@@ -9383,10 +9383,10 @@
         <v>452</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9406,7 +9406,7 @@
         <v>4</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>453</v>
@@ -9415,10 +9415,10 @@
         <v>454</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9438,7 +9438,7 @@
         <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>455</v>
@@ -9447,10 +9447,10 @@
         <v>456</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9470,7 +9470,7 @@
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>457</v>
@@ -9479,10 +9479,10 @@
         <v>458</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9511,10 +9511,10 @@
         <v>460</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9534,7 +9534,7 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>461</v>
@@ -9543,10 +9543,10 @@
         <v>462</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9575,10 +9575,10 @@
         <v>464</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9607,10 +9607,10 @@
         <v>466</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9639,10 +9639,10 @@
         <v>468</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9671,10 +9671,10 @@
         <v>429</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9703,10 +9703,10 @@
         <v>471</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9735,10 +9735,10 @@
         <v>473</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9767,10 +9767,10 @@
         <v>475</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9799,10 +9799,10 @@
         <v>477</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9831,10 +9831,10 @@
         <v>479</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9863,10 +9863,10 @@
         <v>481</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
@@ -730,18 +730,18 @@
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
+    <t xml:space="preserve">5107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
     <t xml:space="preserve">5404</t>
   </si>
   <si>
     <t xml:space="preserve">Petorca</t>
   </si>
   <si>
-    <t xml:space="preserve">5107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
     <t xml:space="preserve">5403</t>
   </si>
   <si>
@@ -2128,7 +2128,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:59</t>
+    <t xml:space="preserve">2026-09-18 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="720">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11302</t>
@@ -97,9 +97,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11101</t>
   </si>
   <si>
@@ -208,7 +205,7 @@
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5504</t>
@@ -235,7 +232,7 @@
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16103</t>
@@ -604,7 +601,7 @@
     <t xml:space="preserve">16206</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">16102</t>
@@ -784,9 +781,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">7106</t>
   </si>
   <si>
@@ -1354,7 +1348,7 @@
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1405</t>
@@ -1474,7 +1468,7 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8202</t>
@@ -1543,7 +1537,7 @@
     <t xml:space="preserve">Tomé</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9101</t>
@@ -1552,7 +1546,7 @@
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14101</t>
@@ -1615,7 +1609,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">10101</t>
@@ -1723,7 +1717,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">10404</t>
@@ -2137,7 +2131,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:15</t>
+    <t xml:space="preserve">2026-10-05 17:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2765,7 +2759,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2794,10 +2788,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -2826,10 +2820,10 @@
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2858,10 +2852,10 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2890,10 +2884,10 @@
         <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2922,10 +2916,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -2954,10 +2948,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -2986,10 +2980,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -3018,10 +3012,10 @@
         <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -3050,10 +3044,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -3082,10 +3076,10 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3114,10 +3108,10 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -3143,19 +3137,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3175,19 +3169,19 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -3207,19 +3201,19 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -3239,19 +3233,19 @@
         <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3271,19 +3265,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3303,19 +3297,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3335,19 +3329,19 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3367,19 +3361,19 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3402,16 +3396,16 @@
         <v>18</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3431,19 +3425,19 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3463,19 +3457,19 @@
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3495,19 +3489,19 @@
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3527,19 +3521,19 @@
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3559,19 +3553,19 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3591,19 +3585,19 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3623,19 +3617,19 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3655,19 +3649,19 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3687,19 +3681,19 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3722,16 +3716,16 @@
         <v>18</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3751,19 +3745,19 @@
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3783,19 +3777,19 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3818,16 +3812,16 @@
         <v>18</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3847,19 +3841,19 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3882,16 +3876,16 @@
         <v>18</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3914,16 +3908,16 @@
         <v>18</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3943,19 +3937,19 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3975,19 +3969,19 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -4010,16 +4004,16 @@
         <v>18</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -4039,19 +4033,19 @@
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4071,25 +4065,25 @@
         <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>74.39</v>
+        <v>74.4</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4103,19 +4097,19 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4138,16 +4132,16 @@
         <v>18</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4167,19 +4161,19 @@
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4199,19 +4193,19 @@
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4231,19 +4225,19 @@
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="F53" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4263,19 +4257,19 @@
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4295,19 +4289,19 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4327,19 +4321,19 @@
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4362,16 +4356,16 @@
         <v>18</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4391,19 +4385,19 @@
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4423,19 +4417,19 @@
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4455,19 +4449,19 @@
         <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4490,16 +4484,16 @@
         <v>18</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4519,19 +4513,19 @@
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4554,16 +4548,16 @@
         <v>18</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4586,16 +4580,16 @@
         <v>18</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4615,19 +4609,19 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="F65" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4647,19 +4641,19 @@
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="F66" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4682,16 +4676,16 @@
         <v>18</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4711,19 +4705,19 @@
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4743,19 +4737,19 @@
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4775,19 +4769,19 @@
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4807,19 +4801,19 @@
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4839,19 +4833,19 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4871,19 +4865,19 @@
         <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4906,16 +4900,16 @@
         <v>18</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4935,19 +4929,19 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="F75" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4967,19 +4961,19 @@
         <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4999,19 +4993,19 @@
         <v>13</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D77" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -5031,19 +5025,19 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5066,16 +5060,16 @@
         <v>18</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5095,19 +5089,19 @@
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5130,16 +5124,16 @@
         <v>18</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="F81" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5162,16 +5156,16 @@
         <v>18</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5191,19 +5185,19 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5223,19 +5217,19 @@
         <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F84" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5255,19 +5249,19 @@
         <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="F85" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5290,16 +5284,16 @@
         <v>18</v>
       </c>
       <c r="D86" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="F86" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5322,16 +5316,16 @@
         <v>18</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="F87" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5351,19 +5345,19 @@
         <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="F88" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5383,19 +5377,19 @@
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="F89" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5415,19 +5409,19 @@
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="F90" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5447,19 +5441,19 @@
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="F91" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5482,16 +5476,16 @@
         <v>18</v>
       </c>
       <c r="D92" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="F92" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5511,19 +5505,19 @@
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="F93" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5543,19 +5537,19 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D94" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5575,19 +5569,19 @@
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="F95" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5607,19 +5601,19 @@
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F96" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5642,16 +5636,16 @@
         <v>18</v>
       </c>
       <c r="D97" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F97" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5671,19 +5665,19 @@
         <v>16</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F98" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5703,19 +5697,19 @@
         <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F99" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5735,19 +5729,19 @@
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="F100" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5767,19 +5761,19 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D101" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F101" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5799,19 +5793,19 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D102" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="F102" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5834,16 +5828,16 @@
         <v>18</v>
       </c>
       <c r="D103" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="F103" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5863,19 +5857,19 @@
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D104" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="F104" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5898,16 +5892,16 @@
         <v>18</v>
       </c>
       <c r="D105" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="F105" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5927,19 +5921,19 @@
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D106" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="F106" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5962,16 +5956,16 @@
         <v>18</v>
       </c>
       <c r="D107" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="F107" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5991,19 +5985,19 @@
         <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D108" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="F108" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -6023,19 +6017,19 @@
         <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D109" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="F109" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6055,19 +6049,19 @@
         <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="F110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6087,19 +6081,19 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D111" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="F111" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6119,19 +6113,19 @@
         <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="F112" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6151,19 +6145,19 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E113" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="F113" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6183,19 +6177,19 @@
         <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D114" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="F114" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6215,19 +6209,19 @@
         <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D115" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="F115" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6247,19 +6241,19 @@
         <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D116" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="F116" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6279,19 +6273,19 @@
         <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="F117" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6311,19 +6305,19 @@
         <v>16</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D118" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="F118" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6343,19 +6337,19 @@
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>255</v>
+        <v>62</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6375,19 +6369,19 @@
         <v>7</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6407,19 +6401,19 @@
         <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6442,16 +6436,16 @@
         <v>18</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6471,19 +6465,19 @@
         <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6503,19 +6497,19 @@
         <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6535,19 +6529,19 @@
         <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6567,19 +6561,19 @@
         <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6599,19 +6593,19 @@
         <v>16</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6631,19 +6625,19 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6663,19 +6657,19 @@
         <v>16</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6695,19 +6689,19 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6727,19 +6721,19 @@
         <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6762,16 +6756,16 @@
         <v>18</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6791,19 +6785,19 @@
         <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6823,19 +6817,19 @@
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6855,19 +6849,19 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6887,19 +6881,19 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6919,19 +6913,19 @@
         <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6951,19 +6945,19 @@
         <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6986,16 +6980,16 @@
         <v>18</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -7015,19 +7009,19 @@
         <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7047,19 +7041,19 @@
         <v>16</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7079,19 +7073,19 @@
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7111,19 +7105,19 @@
         <v>16</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7143,19 +7137,19 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7175,19 +7169,19 @@
         <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7207,19 +7201,19 @@
         <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7242,16 +7236,16 @@
         <v>18</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7271,19 +7265,19 @@
         <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7303,19 +7297,19 @@
         <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7335,19 +7329,19 @@
         <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7367,19 +7361,19 @@
         <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7399,19 +7393,19 @@
         <v>16</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7431,19 +7425,19 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7463,19 +7457,19 @@
         <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7498,16 +7492,16 @@
         <v>18</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7527,19 +7521,19 @@
         <v>16</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7559,19 +7553,19 @@
         <v>16</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7591,19 +7585,19 @@
         <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7623,19 +7617,19 @@
         <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7658,16 +7652,16 @@
         <v>18</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7687,19 +7681,19 @@
         <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7719,19 +7713,19 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7751,19 +7745,19 @@
         <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7783,19 +7777,19 @@
         <v>5</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7815,19 +7809,19 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7847,19 +7841,19 @@
         <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7879,19 +7873,19 @@
         <v>5</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7914,16 +7908,16 @@
         <v>18</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7943,19 +7937,19 @@
         <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7975,19 +7969,19 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -8010,16 +8004,16 @@
         <v>18</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8039,19 +8033,19 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8074,16 +8068,16 @@
         <v>18</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8103,19 +8097,19 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8138,16 +8132,16 @@
         <v>18</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8167,19 +8161,19 @@
         <v>7</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8199,19 +8193,19 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8231,19 +8225,19 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8263,19 +8257,19 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8295,19 +8289,19 @@
         <v>5</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8327,19 +8321,19 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8359,19 +8353,19 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8391,19 +8385,19 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8423,19 +8417,19 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8455,19 +8449,19 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8487,19 +8481,19 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8519,19 +8513,19 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8551,19 +8545,19 @@
         <v>13</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8583,19 +8577,19 @@
         <v>13</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8615,19 +8609,19 @@
         <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8647,19 +8641,19 @@
         <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D191" s="2" t="s">
+      <c r="F191" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E191" s="2" t="s">
+      <c r="G191" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G191" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8679,19 +8673,19 @@
         <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D192" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>405</v>
-      </c>
       <c r="F192" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8711,19 +8705,19 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8743,19 +8737,19 @@
         <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8775,19 +8769,19 @@
         <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8807,19 +8801,19 @@
         <v>15</v>
       </c>
       <c r="C196" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D196" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="F196" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8839,19 +8833,19 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8871,19 +8865,19 @@
         <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8903,19 +8897,19 @@
         <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8935,19 +8929,19 @@
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8967,19 +8961,19 @@
         <v>15</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8999,19 +8993,19 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -9031,19 +9025,19 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9063,19 +9057,19 @@
         <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9095,19 +9089,19 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9127,19 +9121,19 @@
         <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D206" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="F206" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9159,19 +9153,19 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9191,19 +9185,19 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9223,19 +9217,19 @@
         <v>2</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9255,19 +9249,19 @@
         <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9287,19 +9281,19 @@
         <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9319,19 +9313,19 @@
         <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D212" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>447</v>
-      </c>
       <c r="F212" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9351,19 +9345,19 @@
         <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9383,19 +9377,19 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9415,19 +9409,19 @@
         <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9447,19 +9441,19 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9479,19 +9473,19 @@
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9511,19 +9505,19 @@
         <v>3</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9543,19 +9537,19 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9575,19 +9569,19 @@
         <v>1</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9607,19 +9601,19 @@
         <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9639,19 +9633,19 @@
         <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9671,19 +9665,19 @@
         <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9703,19 +9697,19 @@
         <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9735,19 +9729,19 @@
         <v>2</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9767,19 +9761,19 @@
         <v>1</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9799,19 +9793,19 @@
         <v>2</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9831,19 +9825,19 @@
         <v>2</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9863,19 +9857,19 @@
         <v>2</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9895,19 +9889,19 @@
         <v>2</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9927,19 +9921,19 @@
         <v>2</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9959,19 +9953,19 @@
         <v>8</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="F232" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E232" s="2" t="s">
+      <c r="G232" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9991,19 +9985,19 @@
         <v>8</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -10023,19 +10017,19 @@
         <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10055,19 +10049,19 @@
         <v>8</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10087,19 +10081,19 @@
         <v>8</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10119,19 +10113,19 @@
         <v>8</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10151,19 +10145,19 @@
         <v>8</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10183,19 +10177,19 @@
         <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10215,19 +10209,19 @@
         <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10247,19 +10241,19 @@
         <v>8</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10279,19 +10273,19 @@
         <v>9</v>
       </c>
       <c r="C242" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="D242" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="F242" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10311,19 +10305,19 @@
         <v>14</v>
       </c>
       <c r="C243" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="F243" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10343,19 +10337,19 @@
         <v>8</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10375,19 +10369,19 @@
         <v>14</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10407,19 +10401,19 @@
         <v>10</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>520</v>
-      </c>
       <c r="F246" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10439,19 +10433,19 @@
         <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10471,19 +10465,19 @@
         <v>10</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10503,19 +10497,19 @@
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10535,19 +10529,19 @@
         <v>10</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10567,19 +10561,19 @@
         <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10599,19 +10593,19 @@
         <v>8</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10631,19 +10625,19 @@
         <v>10</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10663,19 +10657,19 @@
         <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10695,19 +10689,19 @@
         <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10727,19 +10721,19 @@
         <v>14</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10759,19 +10753,19 @@
         <v>8</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10791,19 +10785,19 @@
         <v>14</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10823,19 +10817,19 @@
         <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10855,19 +10849,19 @@
         <v>8</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10887,19 +10881,19 @@
         <v>9</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10919,19 +10913,19 @@
         <v>14</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10951,19 +10945,19 @@
         <v>8</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -10983,19 +10977,19 @@
         <v>9</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -11015,19 +11009,19 @@
         <v>14</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -11047,19 +11041,19 @@
         <v>8</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11079,19 +11073,19 @@
         <v>10</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11111,19 +11105,19 @@
         <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11143,19 +11137,19 @@
         <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11175,19 +11169,19 @@
         <v>8</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11207,19 +11201,19 @@
         <v>10</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11239,19 +11233,19 @@
         <v>10</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11271,19 +11265,19 @@
         <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11303,19 +11297,19 @@
         <v>8</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11335,19 +11329,19 @@
         <v>8</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11367,19 +11361,19 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11399,19 +11393,19 @@
         <v>9</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11431,19 +11425,19 @@
         <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11463,19 +11457,19 @@
         <v>8</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11495,19 +11489,19 @@
         <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11527,19 +11521,19 @@
         <v>14</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11559,19 +11553,19 @@
         <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11591,19 +11585,19 @@
         <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11623,19 +11617,19 @@
         <v>14</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11655,19 +11649,19 @@
         <v>10</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11687,19 +11681,19 @@
         <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11719,19 +11713,19 @@
         <v>9</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11751,19 +11745,19 @@
         <v>10</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11783,19 +11777,19 @@
         <v>8</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11815,19 +11809,19 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11847,19 +11841,19 @@
         <v>14</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11879,19 +11873,19 @@
         <v>9</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11911,19 +11905,19 @@
         <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11943,19 +11937,19 @@
         <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11975,19 +11969,19 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -12007,19 +12001,19 @@
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -12039,19 +12033,19 @@
         <v>9</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12071,19 +12065,19 @@
         <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12103,19 +12097,19 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12135,19 +12129,19 @@
         <v>8</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12167,19 +12161,19 @@
         <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12199,19 +12193,19 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12231,19 +12225,19 @@
         <v>9</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12263,19 +12257,19 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12295,19 +12289,19 @@
         <v>14</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12327,19 +12321,19 @@
         <v>8</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12359,19 +12353,19 @@
         <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12391,19 +12385,19 @@
         <v>10</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12423,19 +12417,19 @@
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12455,19 +12449,19 @@
         <v>9</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12487,19 +12481,19 @@
         <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12519,19 +12513,19 @@
         <v>8</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12551,19 +12545,19 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12583,19 +12577,19 @@
         <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12615,19 +12609,19 @@
         <v>14</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12647,19 +12641,19 @@
         <v>8</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12679,19 +12673,19 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12711,19 +12705,19 @@
         <v>9</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12743,19 +12737,19 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12775,19 +12769,19 @@
         <v>10</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12807,19 +12801,19 @@
         <v>8</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12839,19 +12833,19 @@
         <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12871,19 +12865,19 @@
         <v>10</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12903,19 +12897,19 @@
         <v>10</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12935,19 +12929,19 @@
         <v>10</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -12967,19 +12961,19 @@
         <v>10</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -12999,19 +12993,19 @@
         <v>14</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -13031,19 +13025,19 @@
         <v>9</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
@@ -13063,19 +13057,19 @@
         <v>10</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
@@ -13095,19 +13089,19 @@
         <v>10</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
@@ -13127,19 +13121,19 @@
         <v>10</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>15</v>
@@ -13159,19 +13153,19 @@
         <v>10</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>15</v>
@@ -13191,19 +13185,19 @@
         <v>9</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H333" s="2" t="s">
         <v>15</v>
@@ -13223,19 +13217,19 @@
         <v>10</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>15</v>
@@ -13255,19 +13249,19 @@
         <v>9</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H335" s="2" t="s">
         <v>15</v>
@@ -13287,19 +13281,19 @@
         <v>8</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>15</v>
@@ -13319,19 +13313,19 @@
         <v>9</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H337" s="2" t="s">
         <v>15</v>
@@ -13351,19 +13345,19 @@
         <v>9</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>15</v>
@@ -13393,7 +13387,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13401,50 +13395,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -13466,21 +13460,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13489,7 +13483,7 @@
         <v>2018</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
